--- a/primary_2026-04-23_report.xlsx
+++ b/primary_2026-04-23_report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,13 +528,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>情绪心理班会课❗把压力管理上成心灵汽水站</t>
+          <t>班会靠疯狂动物城，学生冲突居然少了！谁</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>伊伊学姐</t>
+          <t>亦亦同学！</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -542,11 +542,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2天前</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>328</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -564,7 +564,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>图文结合</t>
+          <t>卡通插画</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>暖色</t>
+          <t>冷色</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -597,7 +597,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>个人认证</t>
+          <t>无认证</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -606,24 +606,24 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>32.8</v>
+        <v>3.6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e5c256000000002003892a?xsec_token=ABuIR9o57oHt2c9N8Gn39Y7_u2TEJX-4In1-8eFnaIIos=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69426cba000000001e03a80b?xsec_token=AB9CY8NVM5SMyOUTUfrBNcGlvxauC_FgKydmzo4Sp2P8U=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>当班级有了暖意，纪律就会很非常稳定！</t>
+          <t>期中考试考前动员会/主题班会🔥🔥</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>徐老师</t>
+          <t>下雪不冷</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -631,11 +631,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6天前</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>848</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>班级管理</t>
+          <t>中考高考</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>黑板报</t>
+          <t>图文结合</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>高级感</t>
+          <t>冷色</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -695,24 +695,24 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>84.8</v>
+        <v>5.7</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e066c6000000001d01cedc?xsec_token=ABe1JH2UIU19UNU6TZZH66P1WfG6AeXa7x7ATblsec6QE=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69080482000000000700c9c6?xsec_token=ABX4ydkxKrjr2vl5cs60ffZ9qSZpfoSkgltrdit3eSPcw=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>情绪管理心理主题班会，学会与情绪共处！</t>
+          <t>当“情绪”来敲门—主题班会</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>小Y老师</t>
+          <t>壹恒壹书</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -720,11 +720,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2天前</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>188</v>
+        <v>2046</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -757,17 +757,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>大字报</t>
+          <t>黑板报</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>卡通手绘</t>
+          <t>专业正式</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>卡通</t>
+          <t>冷色</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -775,7 +775,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>无认证</t>
+          <t>蓝V认证</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -784,24 +784,24 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>18.8</v>
+        <v>204.6</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e5c7170000000023024832?xsec_token=ABuIR9o57oHt2c9N8Gn39Y7_3phq2oiTy0y1pZl7cNn_k=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/66d92ee90000000012011ff9?xsec_token=AB0cn3B9hnFkhB2afWxK3rTf0ox4nVrbwQuNt-vt9P4w4=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>网络安全，你我童行！网络安全教育主题班会</t>
+          <t>速码❗心理课/生命教育《我的生命很特别》</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>锦涵同学</t>
+          <t>伊伊学姐</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -809,11 +809,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>6天前</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>安全教育</t>
+          <t>心理健康</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>卡通插画</t>
+          <t>图文结合</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>活泼可爱</t>
+          <t>治愈系</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>冷色</t>
+          <t>高级感</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>无认证</t>
+          <t>个人认证</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -873,24 +873,24 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>12.8</v>
+        <v>13.4</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/68cd3e2c000000001300e792?xsec_token=ABnhimDq_cYm_XolPABsPhBUQ4j8tpklISkCqHHAxk0d0=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69e1a3ae0000000023016773?xsec_token=ABDqR8gtxOfoYc_caFRKVamdphr3AUPQkenDQyCklmkpQ=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>考后复盘主题班会🔥分数不是终点是成长进度</t>
+          <t>掌控专注力的5把钥匙🔑✊</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>清雅老师课件</t>
+          <t>小米粒</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -898,11 +898,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5天前</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>158</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>励志成长</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -935,17 +935,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>大字报</t>
+          <t>黑板报</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>简约风</t>
+          <t>治愈系</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>卡通</t>
+          <t>高级感</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -962,24 +962,24 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>15.8</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e1ed83000000001a03042f?xsec_token=ABDqR8gtxOfoYc_caFRKVame8BAhud-TPeaEV9y0ymtxE=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/68c27e7c000000001d025529?xsec_token=ABpkbMmNTZkYyzWU1w6ZYp6W2Pf5EBIs7CBuSnmDp9SA4=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>当班级有了暖意，纪律就会非常稳定❗️</t>
+          <t>这节心理课 学生上哭了😭</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>懒羊老师课件</t>
+          <t>momo</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -987,11 +987,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6天前</t>
+          <t>5天前</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>649</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>班级管理</t>
+          <t>心理健康</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>简约风</t>
+          <t>专业正式</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>高级感</t>
+          <t>暖色</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>无认证</t>
+          <t>个人认证</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1051,24 +1051,24 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>64.90000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e07de5000000002102cefb?xsec_token=ABe1JH2UIU19UNU6TZZH66P6O8katdq7tlqv4YpkPhefI=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69e20f93000000001e00f5e6?xsec_token=AB8O0HpZ0fcwg_dIrd8QNJ_tiJc_XVjpjVCbWy5Ds64gg=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>“读书的意义”这样讲，全班学生真的安静了🔥</t>
+          <t>手机管理主题班会｜沉迷手机有真相🔥</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>果冻老师fwh</t>
+          <t>园园老师课件</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1076,11 +1076,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>3天前</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6060</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>班级管理</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>卡通插画</t>
+          <t>黑板报</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>清新自然</t>
+          <t>卡通手绘</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>清新</t>
+          <t>卡通</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1140,24 +1140,24 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>606</v>
+        <v>0.3</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/68f882e70000000004020446?xsec_token=ABpTfZANrCYs2EmAx_38-_vPAHUydgyxO64ztjaMsh2rs=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69e5ca9b000000001b0015e0?xsec_token=ABuIR9o57oHt2c9N8Gn39Y79GJb3UAk5m5lwn20IEgHyQ=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>心理健康主题班会：“我的生命很特别”！！</t>
+          <t>手机管理主题班会：做手机的主人📱</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>芝士</t>
+          <t>柚子坊课件</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5天前</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>145</v>
+        <v>578</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>班级管理</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PPT截图</t>
+          <t>图文结合</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>简约风</t>
+          <t>专业正式</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>暖色</t>
+          <t>清新</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1229,24 +1229,24 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>14.5</v>
+        <v>57.8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e1d71a000000002200f02c?xsec_token=ABDqR8gtxOfoYc_caFRKVamYIR5R921dn6nG-E-Q0YGF0=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/6819dc63000000000c03b131?xsec_token=AB4XmupwzWG5y_LJ_bLGBtpkzcBdu_VSrAMEra5Xgi3ok=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>小学班会课件｜五一假期安全小达人攻略✨</t>
+          <t>情绪心理班会课❗把压力管理上成心灵汽水站</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ye老师</t>
+          <t>伊伊学姐</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2天前</t>
+          <t>3天前</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>安全教育</t>
+          <t>心理健康</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>PPT截图</t>
+          <t>卡通插画</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>专业正式</t>
+          <t>清新自然</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>高级感</t>
+          <t>清新</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1314,28 +1314,28 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>话题""有一定关注度 | 形式：PPT/课件模板型，直接可用</t>
+          <t>话题""有一定关注度</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>33.8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e647650000000022029fb0?xsec_token=ABAn2KR4Xi4rFsMIz_8QfI-oqtKp-1l_eGu6KQgTErthQ=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69e5c256000000002003892a?xsec_token=ABuIR9o57oHt2c9N8Gn39Y7_u2TEJX-4In1-8eFnaIIos=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>手机管理主题班会｜沉迷手机有真相🔥</t>
+          <t>🔥班会爆款｜这节玩笑边界课把霸凌预防讲透</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>园园老师课件</t>
+          <t>小课桌课件</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>班级管理</t>
+          <t>校园霸凌</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>专业正式</t>
+          <t>活泼可爱</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1407,24 +1407,24 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>0.3</v>
+        <v>18.3</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e5ca9b000000001b0015e0?xsec_token=ABuIR9o57oHt2c9N8Gn39Y79GJb3UAk5m5lwn20IEgHyQ=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69e62e390000000021004a11?xsec_token=ABAn2KR4Xi4rFsMIz_8QfI-n1tQfCc1Sp2KgcUTGvQYjs=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>做情绪的小主人心理主题班会PPT</t>
+          <t>治愈系心理班会PPT课件✨我的生命很特别</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PPT设计师星星</t>
+          <t>达克鸭课件库</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1432,11 +1432,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>3天前</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>774</v>
+        <v>143</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>活泼可爱</t>
+          <t>卡通手绘</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>卡通</t>
+          <t>高级感</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1487,33 +1487,33 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>无认证</t>
+          <t>蓝V认证</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>话题""有一定关注度</t>
+          <t>话题""有一定关注度 | 形式：PPT/课件模板型，直接可用</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>77.40000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/693f9a05000000001e006e86?xsec_token=ABg70u_Tekogte02DoTakYj1swzdC6G7CK01xongpoSSw=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69e4a5d600000000230143e4?xsec_token=ABtpd_en-T0eUjLedsHz1LnTIDllrYv86IeV1DD9Khu5s=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>矛盾化解与行为习惯养成主题班会PPT➕教案</t>
+          <t>情绪管理心理主题班会，学会与情绪共处！</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>慧慧老师</t>
+          <t>小Y老师</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1521,11 +1521,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>3天前</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>265</v>
+        <v>193</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>习惯养成</t>
+          <t>心理健康</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>复古风</t>
+          <t>清新自然</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>冷色</t>
+          <t>高级感</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>无认证</t>
+          <t>个人认证</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1585,24 +1585,24 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>26.5</v>
+        <v>19.3</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/695268fa000000001e020ed8?xsec_token=ABUej3qa0DKMLRcehKs_U5ox1182Sg4yDFP90shE7a6VQ=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69e5c7170000000023024832?xsec_token=ABuIR9o57oHt2c9N8Gn39Y7_3phq2oiTy0y1pZl7cNn_k=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>抗挫折主题班会|挫而不折，破茧成蝶(有课件</t>
+          <t>网络安全，你我童行！网络安全教育主题班会</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>乐助文舟</t>
+          <t>锦涵同学</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1610,11 +1610,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>安全教育</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1647,17 +1647,17 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>PPT截图</t>
+          <t>卡通插画</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>复古风</t>
+          <t>清新自然</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>冷色</t>
+          <t>暖色</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -1665,33 +1665,33 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>蓝V认证</t>
+          <t>无认证</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>话题""有一定关注度 | 形式：PPT/课件模板型，直接可用</t>
+          <t>话题""有一定关注度</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>10.5</v>
+        <v>12.8</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69328fed000000001e0388aa?xsec_token=ABK63xl1_7eVebQsVE5GbsDDwMuYVtCnj_5j-YTOIwOZU=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/68cd3e2c000000001300e792?xsec_token=ABnhimDq_cYm_XolPABsPhBUQ4j8tpklISkCqHHAxk0d0=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>考试心理调适主题班会《当考试还剩15分钟》</t>
+          <t>这节心理课，学生上哭了！</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>芝士</t>
+          <t>洛洛老师吖</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1699,11 +1699,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3天前</t>
+          <t>6天前</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>438</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1741,12 +1741,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>卡通手绘</t>
+          <t>专业正式</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>冷色</t>
+          <t>卡通</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>蓝V认证</t>
+          <t>个人认证</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>1.8</v>
+        <v>43.8</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e582960000000021007da7?xsec_token=ABuIR9o57oHt2c9N8Gn39Y7-GeNiQ_wAIjoqgs6iwyyiQ=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69e0c3b9000000002301403e?xsec_token=ABe1JH2UIU19UNU6TZZH66PwBRl8LxYX4nz6VDdYmCR7A=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4.23日读书日主题班会PPT，让学生喜欢读书</t>
+          <t>小学生心理班会封神！看完秒变阳光小超人✨</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>小Y老师</t>
+          <t>W凝</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1788,11 +1788,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2天前</t>
+          <t>1天前</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>心理健康</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1825,17 +1825,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PPT截图</t>
+          <t>实拍场景</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>卡通手绘</t>
+          <t>清新自然</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>高级感</t>
+          <t>冷色</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>个人认证</t>
+          <t>蓝V认证</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1852,24 +1852,24 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e5a8640000000023026fe4?xsec_token=ABuIR9o57oHt2c9N8Gn39Y7xblwRtGK4ouJB_jePMEM4k=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69e828d6000000002102f398?xsec_token=ABtgX8avcevfLOZCulJ4lUJFp1Pkox6THANbVub-MZpSg=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>读书日主题班会｜读书，让你看见更美的世界</t>
+          <t>4.23日读书日主题班会PPT，让学生喜欢读书</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>园园老师课件</t>
+          <t>小Y老师</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>实拍场景</t>
+          <t>PPT截图</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>卡通手绘</t>
+          <t>复古风</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>卡通</t>
+          <t>高级感</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>个人认证</t>
+          <t>蓝V认证</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -1941,24 +1941,24 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e461cf0000000021007ce4?xsec_token=ABtpd_en-T0eUjLedsHz1LnRKYwO-s9YaRpPrehkxkYII=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69e5a8640000000023026fe4?xsec_token=ABuIR9o57oHt2c9N8Gn39Y7xblwRtGK4ouJB_jePMEM4k=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>安全教育主题班会｜五一出游安全要牢记🔥</t>
+          <t>发现闪光点主题班会PPT✨性格优势大探索</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>园园老师课件</t>
+          <t>哆啦B课件</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1966,11 +1966,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3天前</t>
+          <t>7小时前</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>安全教育</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>黑板报</t>
+          <t>PPT截图</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>清新自然</t>
+          <t>复古风</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>冷色</t>
+          <t>卡通</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>无认证</t>
+          <t>蓝V认证</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2030,100 +2030,4550 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/search_result/69e4bdf4000000001b003ee7?xsec_token=ABtpd_en-T0eUjLedsHz1LndEh2nEpb7CneGs4uMBBlsU=&amp;xsec_source=</t>
+          <t>https://www.xiaohongshu.com/search_result/69e95330000000001b022703?xsec_token=ABYpHN2VAMLFxDteDSB5HseIiwOjCnnzoQDx52Ft-ctFg=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>一等奖主题班会 不收藏太亏啦!!</t>
+          <t>矛盾化解与行为习惯养成主题班会PPT➕教案</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
+          <t>慧慧老师</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>270</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>习惯养成</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>治愈系</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>卡通</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>27</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/695268fa000000001e020ed8?xsec_token=ABUej3qa0DKMLRcehKs_U5ox1182Sg4yDFP90shE7a6VQ=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>抗挫折主题班会|挫而不折，破茧成蝶(有课件</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>乐助文舟</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>105</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>治愈系</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度 | 形式：PPT/课件模板型，直接可用</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69328fed000000001e0388aa?xsec_token=ABK63xl1_7eVebQsVE5GbsDDwMuYVtCnj_5j-YTOIwOZU=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>安全教育主题班会｜五一出游安全要牢记🔥</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>园园老师课件</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3天前</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>安全教育</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>黑板报</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>卡通手绘</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69e4bdf4000000001b003ee7?xsec_token=ABtpd_en-T0eUjLedsHz1LndEh2nEpb7CneGs4uMBBlsU=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>考试心理调适主题班会《当考试还剩15分钟》</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>芝士</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3天前</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>18</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>心理健康</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>图文结合</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>治愈系</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>清新</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69e582960000000021007da7?xsec_token=ABuIR9o57oHt2c9N8Gn39Y7-GeNiQ_wAIjoqgs6iwyyiQ=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>自我认知心理课｜《打开我的自信瓶子》</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Happy心理课堂</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>284</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>心理健康</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>纯色背景</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>复古风</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>清新</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69441a85000000001e026038?xsec_token=AB0CHtakUthIqb8J4uPrrEcSdN1cXFAozksqTyQwqRa5E=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>一等奖主题班会 不收藏太亏啦!!</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>融思汇文坊</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>2025-04-21</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>112</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="F24" t="n">
+        <v>111</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>图文帖</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>高年级(5-6)</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>少图(1-3张)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>活泼可爱</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>暖色</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/67b9d396000000001203f680?xsec_token=ABJvxL2HhyEKyZAQz_GvKR-FO79tMapRGcfA_sZP90s80=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>速码❗️把压力变动力的考试压力班会，绝了</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>舒塔备课</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>03-29</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>327</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>心理健康</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>图文结合</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>卡通手绘</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>卡通</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69c8ce58000000001a03570e?xsec_token=AB_n2OIMZKl_-Xl7YhtKhOoZr05skKX9GVhBlIAwXL1vk=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>一节课搞定“学生滥用网络用语”难题</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>猫猫的猫粮Mm</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>04-15</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>38</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>实拍场景</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>专业正式</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>清新</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69df817f0000000023016300?xsec_token=AB-WxKEp5QypreAcYCtM6QIl0Disl8c3NETcSd0c1HFeI=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>拒绝脏话主题班会课件｜拒绝脏话，从心开始</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>园园老师课件</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>04-02</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>55</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>专业正式</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>清新</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度 | 形式：PPT/课件模板型，直接可用</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69ce2e1a0000000023011fcb?xsec_token=AB_dCY3lAeqsTVlkD8gXDXE0BKEdekzDVxpHaGvc8w4S0=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>当班级有了暖意，纪律就会很非常稳定！</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>徐老师</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>04-16</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>852</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>班级管理</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>黑板报</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>复古风</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>暖色</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69e066c6000000001d01cedc?xsec_token=ABe1JH2UIU19UNU6TZZH66P1WfG6AeXa7x7ATblsec6QE=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>孩子犯错总推锅？知错就改主题班会附教案！</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>天天小学课件</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>6天前</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>实拍场景</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>简约风</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度 | 提及"孩子"，情感连接强</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69deff8f0000000023006b23?xsec_token=AB7XrJxfQvYi0xh3x3yRiotFc5VoHcSNLYlz177Icvxsk=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>厉害的老师这样对待课堂碎嘴子</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>宝藏小汐</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>04-01</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1910</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>大字报</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>专业正式</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>191</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69cd172f00000000210389e7?xsec_token=ABsJ-aoyc8Yb7WJgV446P8DcYEp_LZXRXGfp76UgRn3cg=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>小学低段年级‼️好习惯的养成很关键</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>慧慧老师</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>03-26</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>117</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>习惯养成</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>活泼可爱</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69c4dd500000000023015953?xsec_token=ABD_JWI6aeQSC7Y9OdK6m3fMwnBrwgwNqQHEophP0HtT8=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>主题班会:谣言止于智者🔥</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>宝藏小爱</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>28</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>纯色背景</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>卡通手绘</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>高级感</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69365fd2000000001f00ea76?xsec_token=ABr0LOpHqlK81HTboSFI-zddfCEUM8d2kU81LLXRcEhxc=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>那天班会讲了一分钟的价值，学生支棱起来了</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>花卷课件</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>32</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>黑板报</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>治愈系</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>冷色</t>
         </is>
       </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/6940bbcd000000001b023369?xsec_token=AB05ROAYn2hR2ZFCF_EWyJByjQQtxm_krKlBn--2TBQBU=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>我告诉学生如何面对恶意后，班风明显变好了</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>檬檬老师课件</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>105</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>图文结合</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>活泼可爱</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>清新</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/6947bb03000000001e025316?xsec_token=ABzi25o40G3hOiBTyhRNMi5Q-LSPYzjGNtAZ4BJ1l7U5g=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>手机管理主题班会课件｜摆脱手机上瘾🔥</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>园园老师课件</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>04-14</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>班级管理</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>清新自然</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>卡通</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度 | 形式：PPT/课件模板型，直接可用</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69ddff140000000023023e80?xsec_token=ABCZZj_6SMxGVdn9GMDRcKgR4Xltmk46-AEwhDY7N9IRs=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>💡班会课📚：一堂课讲透“刷屏陷阱”</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>备课灯下</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3天前</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>黑板报</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>活泼可爱</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>清新</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>蓝V认证</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>话题""有一定关注度</t>
         </is>
       </c>
-      <c r="T19" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/search_result/67b9d396000000001203f680?xsec_token=ABJvxL2HhyEKyZAQz_GvKR-FO79tMapRGcfA_sZP90s80=&amp;xsec_source=</t>
+      <c r="T36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69d75ede00000000230237d8?xsec_token=AB4jDNL-ZIFWbw7L5sUpIhLmWoVWtVJOQdgbP5rCfJx7E=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>班主任开【快乐学习，高效学习】主题班会</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>嘉果的资料箱</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>学习方法</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>黑板报</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>复古风</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>卡通</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/694f87e20000000022031bed?xsec_token=ABxJ8srgx9fa3fT3XrxRVmn7or-iU-9FohyRPA8eiyY8A=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>没考好别灰心‼️路还长慢慢走🌸考后状态调节</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>慧慧老师</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>13</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>大字报</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>清新自然</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>卡通</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/6808b255000000001c0028bd?xsec_token=ABUsZ6tXQ8ukS4mLfYC9sMxkm3wP-2BSgZx_1kvPAlQ4I=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>用哪吒精神开启新学期开学第一课</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>小红薯676C425E</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>107</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>实拍场景</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>复古风</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>暖色</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/67a317bc0000000029026bd8?xsec_token=ABJGRV7weiocWOYb8HYJI3np8tTDvYgQmQ31jtVot_-mI=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>《爱你老己，明天见》心理健康主题班会课件</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>八爪课件店铺</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>885</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>心理健康</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>简约风</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度 | 形式：PPT/课件模板型，直接可用</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/694ca100000000001e02ee8c?xsec_token=ABqVtr4xSxWJ0YY8thm5aJR74bkbuImowQULe5jBhegCo=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>专治“推延症”主题班会公开课课件ppt</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>大梦想家咖啡豆</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>103</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>卡通手绘</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>卡通</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度 | 形式：PPT/课件模板型，直接可用</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/680d90f4000000001c014d7c?xsec_token=ABUM1o4qwr3do6U9kuyqUit6-WT7Z-uAyP68nd7N8ge9k=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>🌽小学五一劳动节主题班会｜PPT + 逐字稿</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>师友力MAX</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>昨天 17:29</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>复古风</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>卡通</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69e83cb10000000020038bc0?xsec_token=ABtgX8avcevfLOZCulJ4lUJCNwC5Kzzehw3hVKMgJ_LD8=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>心理老师私藏的班会PPT，拯救自卑内耗孩子</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>壹课</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>04-15</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>96</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>心理健康</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>复古风</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度 | 提及"孩子"，情感连接强</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69d7a4d4000000002102c25f?xsec_token=AB4jDNL-ZIFWbw7L5sUpIhLiX_Ic57QVlrLl5YZY0EGmI=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>夸爆了💥‖小学主题班会课-我的抽屉我做主</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>快乐玥玥的班会PPT</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>03-29</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>20</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>大字报</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>简约风</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>高级感</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69c909e60000000022024a1c?xsec_token=ABW49cIIqIKEqJF0Spgm-HFGgSf-8DoqZN_mArGR3wfH0=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>面对欺凌，拒绝沉默🥊小学预防校园欺凌班会</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>慧慧老师</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>04-14</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>57</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>校园霸凌</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>卡通手绘</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>卡通</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69de01a3000000002202b8c5?xsec_token=AB7XrJxfQvYi0xh3x3yRiotJ4QbRn4z3RmuFydquy16rU=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>当班级有了暖意，纪律就会非常稳定❗️</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>懒羊老师课件</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>04-16</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>670</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>班级管理</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>黑板报</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>专业正式</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>暖色</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>67</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69e07de5000000002102cefb?xsec_token=ABe1JH2UIU19UNU6TZZH66P6O8katdq7tlqv4YpkPhefI=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>班会课上 我让学生列了一个清单🔥</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>班主任晓婷老师</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>04-14</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1124</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>纯色背景</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>活泼可爱</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69bfc406000000001b020b94?xsec_token=ABO4x27ntVe1I8xwdMEtMdoqLIGW5bld6vpwzX-0s_eY8=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>班主任请备下这节“反校园欺凌”主题班会课</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>校园PPT</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>03-26</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>7</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>校园霸凌</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>图文结合</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>活泼可爱</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>清新</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69c54741000000001a030177?xsec_token=ABaK0jPYy0HKTeLCM99INs2F__zbRb7yZT_YVvNeMAniE=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>期中复盘！告别差不多，班会直接用🔥</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>学霸英语补给站</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>04-15</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>卡通插画</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>治愈系</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>高级感</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69df910c000000001a027246?xsec_token=AB-WxKEp5QypreAcYCtM6QIsSdHMsemxEGCWbG-C98o3g=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>一分钟价值主题班会改善班风懒散现象</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>潇潇老师呀</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3天前</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>简约风</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69e4c9d60000000023020c7e?xsec_token=ABtpd_en-T0eUjLedsHz1LnUHY-rrlQ4ktZyYYCCCZJOc=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>厉害的班主任让学生“内卷”起来的绝招</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>元宝爆爆</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>04-10</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>纯色背景</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>卡通手绘</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>暖色</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69d8aa73000000001a02426f?xsec_token=ABj4FVX7xZpWqSfJKuVKtp6ASSm2jYn1H7S7BeQbX4TNA=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>太真实了！这都是大多数小学班主任的困扰</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>刘刘刘老师</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>87</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>实拍场景</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>专业正式</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T52" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/692a9ae0000000001e02688b?xsec_token=ABB_aCf373_E2n8m_IdO73NXvmpH7CdQ97z7XHOOzg7yA=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>主题班会：远离“背后蛐蛐”，建设友爱班风</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>周周学姐</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>04-07</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>纯色背景</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>复古风</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>暖色</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69d4d83e000000002301eb45?xsec_token=ABo9_frrJr8WE4DtXTfvLYF53mwGZ-xqIJmvYwdncawCM=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>告别拖延症行动指南！小学生告别摆烂班会课</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>天天小学课件</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3天前</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>黑板报</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>简约风</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69df25c8000000001b0028b5?xsec_token=AB-WxKEp5QypreAcYCtM6QIg5uNFIHqbUqcB02Xf-bXLo=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>学生觉醒学习力的主题班会课件💪</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>茉莉花茶co</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>昨天 16:57</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>学习方法</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>活泼可爱</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度 | 形式：PPT/课件模板型，直接可用</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69e88d61000000002301686f?xsec_token=ABtgX8avcevfLOZCulJ4lUJOpmUg8gvqIuiEcpBHJCLKk=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>“输”得起，才“赢”得起｜培养孩子抗挫力</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>莀汐爱学习</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>04-05</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>卡通插画</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>简约风</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>清新</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度 | 提及"孩子"，情感连接强</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69d22c81000000001d019762?xsec_token=ABX5m3S4S741Gu60oSEtqZM-MJmamdkDuIQGqj2HsZAgI=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>考后心态调整主题班会：分数不是终点</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>柚子坊课件</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1160</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>黑板报</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>治愈系</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>116</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/6800c2c2000000000b01cd3b?xsec_token=ABtYy3_bupz3TiUwf4HDE3pOo0Bi8qoiyAaeHMBC9qF60=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>这是老娘认为心理健康课最棒的课没有之一</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>是芝士酱啊</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>04-02</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>154</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>心理健康</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>大字报</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>卡通手绘</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69cd67670000000023022d7b?xsec_token=ABsJ-aoyc8Yb7WJgV446P8DRqcKybeIkQlmkFdROr5910=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>“读书的意义”这样讲，全班学生真的安静了🔥</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>果冻老师fwh</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>6060</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>纯色背景</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>卡通手绘</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T59" t="n">
+        <v>606</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/68f882e70000000004020446?xsec_token=ABpTfZANrCYs2EmAx_38-_vPAHUydgyxO64ztjaMsh2rs=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>班主任基本功大赛一等奖🏅主题班会</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>方圆老师</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1191</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>黑板报</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>复古风</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>高级感</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T60" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/682027330000000022034700?xsec_token=ABbIuILFNFE-ycs0XmfnJ6kT5b0uEY0_Wp9_R2Lz80XDA=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>当班级有了暖意，纪律就会很稳定！</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>沐然老师</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>6天前</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>378</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>班级管理</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>黑板报</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>治愈系</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>清新</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T61" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69e1bb75000000001a02e8f7?xsec_token=ABDqR8gtxOfoYc_caFRKVamZZxsaqmhlXFhemU_VA-EHg=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>毕业前最后一次班会｜不负遇见，勇敢向前</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>班主任课件</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>140</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>黑板报</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>复古风</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>高级感</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T62" t="n">
+        <v>14</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/681dab5e000000002202b063?xsec_token=ABy76CB_Rr_yixICjbq6-W_8MzqZLrZG00V8Q8IZkTPG8=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>班主任必看！没有规矩，不成方圆主题班会</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>猫与盐湖</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>41</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>大字报</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>治愈系</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>高级感</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T63" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/68ff9e730000000007014451?xsec_token=AB7L6yMv1UkjpXYqy1WNMEUEqXoHgoCk1KiXb3BG6ycxo=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>小学成长主题班会课件：培养敢提问的孩子</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>莀汐爱学习</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>04-06</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>励志成长</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>治愈系</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>卡通</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度 | 形式：PPT/课件模板型，直接可用 | 提及"孩子"，情感连接强</t>
+        </is>
+      </c>
+      <c r="T64" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69d39c0400000000230249ad?xsec_token=ABHfdf7EQwFg3qeih3tGSrLCi0r_2oDU9RBWkkTQehf0w=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>拒绝内耗！《慢一点也没关系》主题班会PPT</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>萱萱老师sou</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>04-07</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>36</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>卡通手绘</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>清新</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T65" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69d4d47a000000001d01c5e8?xsec_token=ABo9_frrJr8WE4DtXTfvLYF55y577kcSwZUxYz96vk15A=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>拒绝内耗，拥抱阳光❤️心理健康主题班会</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>慧慧老师</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>6天前</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>85</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>心理健康</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>实拍场景</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>治愈系</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T66" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69e0ac81000000001f00102a?xsec_token=ABe1JH2UIU19UNU6TZZH66P4C_da2TQ4tx8kLk_h-eRaA=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>小学心理课带教案、逐字稿</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>吾离小铺</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>04-07</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>395</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>心理健康</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>图文结合</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>治愈系</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>个人认证</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T67" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69d4d7410000000021012dcf?xsec_token=ABo9_frrJr8WE4DtXTfvLYFxa9IVROGs2ZUfCN9x0a1Hs=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>主题班会校园安全无小事，交通安全要牢记</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>米可爱学习</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>3天前</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>安全教育</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>简约风</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>冷色</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>蓝V认证</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69e58779000000001a02543f?xsec_token=ABuIR9o57oHt2c9N8Gn39Y71mZ7P65c3hBo-tq4KbBKqI=&amp;xsec_source=</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>上完生命教育课，学生都哭了</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>好柿花生🥜</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>04-15</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>297</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>图文帖</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>高年级(5-6)</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>少图(1-3张)</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>PPT截图</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>活泼可爱</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>暖色</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>无认证</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>话题""有一定关注度</t>
+        </is>
+      </c>
+      <c r="T69" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/search_result/69df66a3000000001a021204?xsec_token=AB-WxKEp5QypreAcYCtM6QIlLfrJMmBwYiE5dqLkpwOwA=&amp;xsec_source=</t>
         </is>
       </c>
     </row>
@@ -2160,7 +6610,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -2170,7 +6620,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -2180,7 +6630,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>538.0555555555555</v>
+        <v>321.7794117647059</v>
       </c>
     </row>
     <row r="5">
@@ -2224,7 +6674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2242,21 +6692,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>心理健康</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -2266,13 +6716,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>安全教育</t>
+          <t>校园霸凌</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2282,11 +6732,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>励志成长</t>
+          <t>安全教育</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2296,6 +6746,36 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>学习方法</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>中考高考</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>励志成长</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
     </row>
